--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,146 +441,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>ASST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>ABCL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>KLAC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>CBRS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IOVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ISRG</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QMCO</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NTAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MXL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TEM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SDGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QUBT</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>USDE</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>STRC</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>OUST</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SECZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ILMN</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GLND</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>COIN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,198 +441,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>FRSH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SDEV</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDLN</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ALAB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>GTLB</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>ASST</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>GTLB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>FPS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>AXTI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NVAX</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>COHR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NTNX</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MXL</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TRMD</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PACB</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>XRPN</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NBIS</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SDGR</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>SKHY</t>
+          <t>CRWD</t>
         </is>
       </c>
     </row>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -771,7 +771,11 @@
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BTSG</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>NTRA</t>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,346 +441,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>ECHO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>PENG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NXT</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GTLB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>MAT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>VYLR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NVAX</t>
+          <t>SUNB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GMAB</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IOVA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NTSK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MAT</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ISRG</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>HAS</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>OPCH</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>RXRX</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>KOD</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PANW</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>NTNX</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>STNE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NTAP</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>OKTA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>QTEX</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>GTLB</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PCVX</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SUNB</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ILMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SHLS</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>VYLR</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>MDLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SNPS</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>BTSG</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NTRA</t>
-        </is>
-      </c>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -456,137 +456,111 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>BORR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>PLTR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EBAY</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PANW</t>
-        </is>
-      </c>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>SUNB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EXEL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TRMD</t>
-        </is>
-      </c>
+          <t>OPCH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>MRNA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SPCX</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>GMAB</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VYLR</t>
-        </is>
-      </c>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FRSH</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SUNB</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>OKTA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NTSK</t>
-        </is>
-      </c>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AFRM</t>
-        </is>
-      </c>
+          <t>PENG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>INTR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -449,118 +449,26 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>GOOG</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BORR</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GTLB</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>IBRX</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SUNB</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LYFT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>OPCH</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>INTR</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>BMBL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -441,32 +441,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>AAPL</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BMBL</t>
-        </is>
-      </c>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
     </row>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,19 +444,443 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PDD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AVTR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BORR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PTON</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DBX</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ARQT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CDNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AEP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FRSH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ASO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>GMAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GEHC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BRZE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HTFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BIIB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IOVA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CAKE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>INTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BSY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MDLN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MRNA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CCEP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CME</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PCVX</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>OPCH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CTAS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PENG</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DOCU</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NVAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EXEL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EXLS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VYLR</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GTLB</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HAS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HTHT</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IBRX</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WLTH</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ISRG</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KDP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LAUR</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LIN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MDLZ</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NAVN</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NTAP</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RELY</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>OLLI</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>OTEX</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>VSXY</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>STRC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ACHC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,61 +446,61 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BORR</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PTON</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CCEP</t>
         </is>
       </c>
     </row>
@@ -512,375 +512,261 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>CME</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>TCRT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>COR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>VSXY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>CSGP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>BORR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MDLN</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CCC</t>
-        </is>
-      </c>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CDW</t>
-        </is>
-      </c>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>HTHT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MTCH</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CME</t>
-        </is>
-      </c>
+          <t>CTAS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PCVX</t>
+          <t>MDLZ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OPCH</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CTAS</t>
-        </is>
-      </c>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>NAVN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>DOCU</t>
-        </is>
-      </c>
+          <t>FANG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NVAX</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>EXEL</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>HAS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VYLR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>EXLS</t>
-        </is>
-      </c>
+          <t>KDP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VYLR</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GTLB</t>
-        </is>
-      </c>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SHOP</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>HTHT</t>
-        </is>
-      </c>
+          <t>NCPL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WLTH</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ISRG</t>
-        </is>
-      </c>
+          <t>TECH</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KDP</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LAUR</t>
-        </is>
-      </c>
+          <t>BMBL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LYFT</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>NAVN</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>NTAP</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>RELY</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>OLLI</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SSNC</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>OTEX</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>VSXY</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>STRC</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ACHC</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,7 +690,11 @@
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -704,7 +708,11 @@
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ARQT</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -723,7 +731,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -740,33 +748,19 @@
           <t>BMBL</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>EBAY</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>OTEX</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,100 +441,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EXE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>GMAB</t>
-        </is>
-      </c>
+          <t>BRZE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>APA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>KDP</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ARQT</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CSX</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
           <t>HAS</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LYFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ISRG</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MNST</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TCRT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CTSH</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,22 +439,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BRZE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IOVA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>MRNA</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HAS</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,24 +439,22 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IOVA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>KDP</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,427 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>ACGL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>CSX</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PODD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AZN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HONA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BRZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BSP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ODFL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AEP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PECO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EXEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AMCR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CME</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTEN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EXE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ASO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FRSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>APPN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BSY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GEHC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KMB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>IRON</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CCEP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CSGP</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PEGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MNST</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CTAS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PAGP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RPRX</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DBX</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DOCU</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EXC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EVRG</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TENB</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ISRG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EXLS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NDAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LIN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AVTR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ORLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LNT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GMAB</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MRSH</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HAS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NCNO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NWSA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
         <is>
           <t>KDP</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SGRY</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SUNB</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MDLZ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -441,34 +441,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>COCO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>CELH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,36 +478,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>NXPI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>PTEN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -517,339 +517,319 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>SOLS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>CHKP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>CTAS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>EXE</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ASO</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>INTR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>HCSG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>PAA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SLDE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>CSGP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>NAVN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>AMCR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>NRIX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EVRG</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EXLS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NDAQ</t>
-        </is>
-      </c>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FOXA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ORLY</t>
-        </is>
-      </c>
+          <t>RELY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LNT</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GMAB</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>PAA</t>
-        </is>
-      </c>
+          <t>TENB</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MRSH</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>VSXY</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SLN</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HAS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>SSNC</t>
-        </is>
-      </c>
+          <t>CME</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NCNO</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INTU</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
+          <t>MRSH</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KDP</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>HALO</t>
-        </is>
-      </c>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -857,15 +837,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>MDLZ</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
     </row>
   </sheetData>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>CART</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>CDW</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>CTAS</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>DBX</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HCSG</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>ERIC</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>HCSG</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>HTFL</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>ISRG</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -718,7 +718,11 @@
           <t>MTCH</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PAGP</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -726,17 +730,17 @@
           <t>SHOP</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>PTC</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>RPRX</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -744,17 +748,17 @@
           <t>TEAM</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RELY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>FISV</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>RELY</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -762,17 +766,17 @@
           <t>TW</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ADP</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TENB</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -780,14 +784,10 @@
           <t>VSXY</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SLN</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -795,13 +795,13 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -809,13 +809,13 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -823,13 +823,13 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>SLN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -837,7 +837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,408 +441,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>SGRY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>NXPI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ASST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>TNGX</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APPN</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BSY</t>
-        </is>
-      </c>
+          <t>ERIC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>GTLB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CHKP</t>
-        </is>
-      </c>
+          <t>GMAB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SOLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BZ</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>GMAB</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DOCU</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CART</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>EBAY</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>INTR</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>EXE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CDW</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GTLB</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NTSK</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>FANG</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CTAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HALO</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PAA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>FRSH</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>DBX</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IOVA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GEHC</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ERIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IRON</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>AMCR</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>HAS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HCSG</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>HON</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HTFL</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NAVN</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CME</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LIFE</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ISRG</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NRIX</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CTSH</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MTCH</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PAGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>RPRX</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>RELY</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>FISV</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SLDE</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>INTU</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>VSXY</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>EXLS</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>KMB</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ADP</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SLN</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CSGP</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MRSH</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t>BRZE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,80 +441,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NXPI</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GILD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TNGX</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ERIC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PEGA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>GTLB</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
           <t>GMAB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>BRZE</t>
         </is>
       </c>
     </row>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,22 +441,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>GMAB</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IOVA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EXC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>GEHC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>CSX</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>GMAB</t>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FITB</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SBUX</t>
         </is>
       </c>
     </row>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,29 +446,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>CPRT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BBIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>MFIC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,25 +478,73 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>SIRI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HBAN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>CSX</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>FITB</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SBUX</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MNST</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AIOK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GEHC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SGRY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PGY</t>
         </is>
       </c>
     </row>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,110 +441,168 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>AZN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FISV</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>BBIO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MFIC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EXC</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SIRI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SIRI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CPRT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AIOK</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PGY</t>
+          <t>GMAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KHC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NXPI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MNST</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NTSK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RXRX</t>
         </is>
       </c>
     </row>

--- a/results/momentum_latest.xlsx
+++ b/results/momentum_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,170 +441,602 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ABCL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AMRX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CHDN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>HBAN</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SNY</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AZN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BBIO</t>
+          <t>RARE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SIRI</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>EXTR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>SOLS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>ADPT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>AXGN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CPB</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>BZ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>PATK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>CME</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>CPRT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LNT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>AMCR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BSY</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VMRK</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>COLM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LFST</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AZN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EXLS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CPB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NRIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BBIO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OZK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BSP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NCNO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PODD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NTSK</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SIRI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ERIC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AIOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SFNC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EVRG</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AVPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CTAS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EXEL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SGRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EXC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FANG</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GEHC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GTLB</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HTHT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>KHC</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ISRG</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LEGN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KDP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LIN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KMB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MANH</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LNT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MNST</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NDAQ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MRSH</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NTLA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PAA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>OSW</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PTEN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ROP</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>REPL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>RPRX</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SDGR</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>RXRX</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TENB</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SNY</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>LULU</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>OKTA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>RXRX</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SUNB</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
